--- a/config/role_logo.xlsx
+++ b/config/role_logo.xlsx
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>調査員</t>
+          <t>调查员</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>立絵解放後に使用可能</t>
+          <t>立绘解放后可以使用</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>調査員</t>
+          <t>调查员</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>立絵解放後に使用可能</t>
+          <t>立绘解放后可以使用</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>ナツミ</t>
+          <t>夏美</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>ナツミ-制服</t>
+          <t>夏美-制服</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="M93" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>ナツミ-水着</t>
+          <t>夏天-泳装</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="M94" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>リコ</t>
+          <t>是从</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="M95" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>リコ-戦闘</t>
+          <t>里科-战斗</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="M96" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>リコ-日常</t>
+          <t>里科-日常</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="M97" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>モカ</t>
+          <t>摩卡咖啡</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="M98" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>モカ-制服</t>
+          <t>摩卡-制服</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>モカ-騎士</t>
+          <t>摩卡骑士</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="M100" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>グレイ</t>
+          <t>灰色</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="M101" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>グレイ-正装</t>
+          <t>灰色-正装</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="M103" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>レイ</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="M106" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>レイ-制服</t>
+          <t>雷-制服</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="M107" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>リクト</t>
+          <t>陆斗</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="M110" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>リクト-戦闘</t>
+          <t>陆地-战斗</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="M111" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>サキ</t>
+          <t>萨基</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>サキ-日常</t>
+          <t>萨基-日常</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="M113" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>チヨ</t>
+          <t>友谊</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="M114" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>チヨ-和服</t>
+          <t>和服-和服</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="M115" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>ルナ</t>
+          <t>露娜</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="M116" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>ルナ-正装</t>
+          <t>露娜-正装</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="M117" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>ルナ-水着</t>
+          <t>露娜-泳装</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="M118" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>リサ</t>
+          <t>丽莎</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="M119" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>リサ-水着</t>
+          <t>丽莎-泳装</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="M120" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>ミキ</t>
+          <t>蛋</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="M121" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>ミキ-制服</t>
+          <t>米奇-制服</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="M122" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>ミキ-日常</t>
+          <t>米奇-日常</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="M123" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>リック</t>
+          <t>里克</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="M124" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>リック-正装</t>
+          <t>里克-正装</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>リック-水着</t>
+          <t>里克-泳装</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="M126" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>スイ</t>
+          <t>主持</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="M127" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>スイ-聖夜</t>
+          <t>圣诞夜</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="M128" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>スイ-水着</t>
+          <t>泳装-泳装</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="M129" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>セイラ</t>
+          <t>塞拉</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="M137" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>セイラ-制服</t>
+          <t>塞拉-制服</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M138" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>セイラ-魅惑</t>
+          <t>塞拉-魅惑</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="M139" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>ロイ</t>
+          <t>路易</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="M140" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>ロイ-戦闘</t>
+          <t>罗伊-战斗</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="M141" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>ロイ-正装</t>
+          <t>罗伊-正装</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M142" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>フラン</t>
+          <t>法郎</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M143" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>フラン-魅惑</t>
+          <t>弗兰-迷人</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M144" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>フラン-正装</t>
+          <t>弗兰-正装</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M145" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>トウマ</t>
+          <t>冬马</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M146" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>トウマ-日常</t>
+          <t>托马-日常</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M147" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>雪</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="M148" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>ユキ-船長</t>
+          <t>雪-船长</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M149" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>ユキ-水着</t>
+          <t>雪-泳装</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M150" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>メグ</t>
+          <t>梅格</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="M153" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>メグ-青蛇</t>
+          <t>梅格-青蛇</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="M154" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>マコ</t>
+          <t>mako</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="M155" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>マコ-制服</t>
+          <t>马科-制服</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="M156" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>マコ-妖狐</t>
+          <t>魔狐-妖狐</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="M157" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>マコ-妖霊</t>
+          <t>魔灵-魔灵</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="M158" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>マホ</t>
+          <t>真帆</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="M159" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>マホ-水着</t>
+          <t>马霍-泳装</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="M160" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>サクラ</t>
+          <t>樱花</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="M165" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>サクラ-制服</t>
+          <t>樱花-制服</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="M166" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>ベン</t>
+          <t>本</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="M167" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>ベン-日常</t>
+          <t>本-日常</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="M168" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>风筝</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M174" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>カイト-正装</t>
+          <t>凯特-正装</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="M175" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>カリナ</t>
+          <t>卡利纳</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="M178" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>カリナ-魅惑</t>
+          <t>卡里娜-魅力</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="M179" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>カリナ-水着</t>
+          <t>卡里娜-泳装</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="M180" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>アリサ</t>
+          <t>艾丽莎</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="M181" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>アリサ-魅惑</t>
+          <t>艾丽莎-魅惑</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="M182" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>アリサ-女神</t>
+          <t>艾丽莎-女神</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="M183" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>ロナ-メイド</t>
+          <t>罗娜-女仆</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="M188" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>テオス</t>
+          <t>特奥斯</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="M193" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>エリサ</t>
+          <t>艾丽莎</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="M194" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>エリサ-制服</t>
+          <t>伊利莎-制服</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="M195" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>エリサ-聖女</t>
+          <t>伊利莎-圣女</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="M196" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>カエデ</t>
+          <t>枫</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="M197" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>カエデ-聖夜</t>
+          <t>枫树-圣诞夜</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="M198" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>カエデ-魅惑</t>
+          <t>枫树-迷人</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M199" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>ナナミ</t>
+          <t>七浪</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="M200" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>ナナミ-審判</t>
+          <t>娜娜美-裁判</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="M201" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>ナナミ-水着</t>
+          <t>娜娜美-泳装</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="M202" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -13585,7 +13585,7 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>レイナ</t>
+          <t>雷纳</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="M207" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>レイナ-戦闘</t>
+          <t>雷纳-战斗</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>レイナ-正装</t>
+          <t>蕾娜-正装</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="M209" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>マリ</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="M213" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>マリ-水着</t>
+          <t>玛丽-泳装</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>ハナ-水着</t>
+          <t>哈娜-泳装</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>ハナ-魅惑</t>
+          <t>花-魅惑</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>ハナ</t>
+          <t>hana</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>ミホ</t>
+          <t>美</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>ミホ-水着</t>
+          <t>美穗-泳装</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="M226" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>ミホ-日常</t>
+          <t>美穗-日常</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>ミホ-女王</t>
+          <t>美穗-女王</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="M228" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>アンナ</t>
+          <t>安娜</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="M229" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>アンナ-日常</t>
+          <t>安娜-日常</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="M230" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>アンナ-正装</t>
+          <t>安娜-礼服</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="M231" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>モモ</t>
+          <t>桃子</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="M236" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>モモ-制服</t>
+          <t>桃子-制服</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="M237" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>モモ-日常</t>
+          <t>桃子-日常</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="M238" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>ダリア</t>
+          <t>大丽花</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="M245" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>ダリア-日常</t>
+          <t>大丽花-日常</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="M246" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>シエル</t>
+          <t>夏尔</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="M260" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t>シエル-日常</t>
+          <t>夏尔-日常</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="M261" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -16941,7 +16941,7 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>シエル-正装</t>
+          <t>夏尔-正装</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="M262" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>ノア</t>
+          <t>诺亚</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="M263" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>ノア-正装</t>
+          <t>诺亚-礼服</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -17142,7 +17142,7 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>ノア-魅惑</t>
+          <t>诺亚-魅惑</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="M265" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>ハルト</t>
+          <t>哈尔特</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>ハルト-日常</t>
+          <t>哈尔特-日常</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -17626,7 +17626,7 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>ハルト-正装</t>
+          <t>哈尔特-正装</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -17693,7 +17693,7 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>ナコ</t>
+          <t>奈子</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>ナコ-水着</t>
+          <t>奈子-泳装</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17795,7 +17795,7 @@
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>ナコ-戦闘</t>
+          <t>纳科-战斗</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -18350,7 +18350,7 @@
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>エル</t>
+          <t>埃尔</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -18385,7 +18385,7 @@
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>エル-船長</t>
+          <t>艾尔-船长</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -18452,7 +18452,7 @@
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>エル-正装</t>
+          <t>艾尔-正装</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>タクヤ</t>
+          <t>拓也</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="M302" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -19416,7 +19416,7 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>タクヤ-正装</t>
+          <t>拓也-正装</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="M303" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>我爱你</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19689,7 +19689,7 @@
       </c>
       <c r="M307" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>アイ-日常</t>
+          <t>爱-日常</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="M308" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>アイ-水着</t>
+          <t>爱-泳装</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="M309" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t>ユウリ</t>
+          <t>游离</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="M310" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t>ユウリ-水着</t>
+          <t>优衣-泳衣</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19957,7 +19957,7 @@
       </c>
       <c r="M311" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑</t>
+          <t>有利-魅惑</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="M312" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>レオ</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -20091,7 +20091,7 @@
       </c>
       <c r="M313" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -20123,7 +20123,7 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>レオ-戦闘</t>
+          <t>莱奥-战斗</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -20158,7 +20158,7 @@
       </c>
       <c r="M314" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>レオ-正装</t>
+          <t>莱奥-正装</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="M315" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>ノゾミ</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="M316" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>ノゾミ-日常</t>
+          <t>愿望-日常</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="M317" s="1" t="inlineStr">
         <is>
-          <t>図鑑解放後に使用可能</t>
+          <t>图鉴解放后可以使用</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>シオン</t>
+          <t>锡安</t>
         </is>
       </c>
       <c r="C484" s="1" t="inlineStr">
@@ -29279,7 +29279,7 @@
       </c>
       <c r="M484" s="1" t="inlineStr">
         <is>
-          <t>アイコン獲得後に使用可能</t>
+          <t>获得图标后即可使用</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -29309,7 +29309,7 @@
       </c>
       <c r="B485" s="1" t="inlineStr">
         <is>
-          <t>セイラ</t>
+          <t>塞拉</t>
         </is>
       </c>
       <c r="C485" s="1" t="inlineStr">
@@ -29342,7 +29342,7 @@
       </c>
       <c r="M485" s="1" t="inlineStr">
         <is>
-          <t>アイコン獲得後に使用可能</t>
+          <t>获得图标后即可使用</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t>マコ</t>
+          <t>mako</t>
         </is>
       </c>
       <c r="C486" s="1" t="inlineStr">
@@ -29405,7 +29405,7 @@
       </c>
       <c r="M486" s="1" t="inlineStr">
         <is>
-          <t>アイコン獲得後に使用可能</t>
+          <t>获得图标后即可使用</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -29435,7 +29435,7 @@
       </c>
       <c r="B487" s="1" t="inlineStr">
         <is>
-          <t>ナギサ</t>
+          <t>渚</t>
         </is>
       </c>
       <c r="C487" s="1" t="inlineStr">
@@ -29468,7 +29468,7 @@
       </c>
       <c r="M487" s="1" t="inlineStr">
         <is>
-          <t>アイコン獲得後に使用可能</t>
+          <t>获得图标后即可使用</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -29498,7 +29498,7 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>ルミナ</t>
+          <t>鲁米娜</t>
         </is>
       </c>
       <c r="C488" s="1" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="M488" s="1" t="inlineStr">
         <is>
-          <t>アイコン獲得後に使用可能</t>
+          <t>获得图标后即可使用</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -29561,7 +29561,7 @@
       </c>
       <c r="B489" s="1" t="inlineStr">
         <is>
-          <t>ミホ</t>
+          <t>美</t>
         </is>
       </c>
       <c r="C489" s="1" t="inlineStr">
@@ -29594,7 +29594,7 @@
       </c>
       <c r="M489" s="1" t="inlineStr">
         <is>
-          <t>アイコン獲得後に使用可能</t>
+          <t>获得图标后即可使用</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
